--- a/output/pdf_financials_xlsx/ODV.xlsx
+++ b/output/pdf_financials_xlsx/ODV.xlsx
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.000909</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>-0.051266</v>
@@ -7397,19 +7397,19 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.646637</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.456553</v>
+        <v>-1.690728</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.05</v>
+        <v>0.000892</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.165833</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>3.20673</v>
+        <v>3.152238</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -7424,10 +7424,10 @@
         <v>1e-06</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-2.118</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-8.917</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>-17.121</v>
@@ -45344,7 +45344,11 @@
           <t>Exploration and evaluation expenses</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -52584,7 +52588,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -53054,7 +53062,11 @@
           <t>Exploration advance payment applied to exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -54394,7 +54406,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -58138,7 +58154,11 @@
           <t>Prepaid and deposit</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E523" s="5" t="n">
         <v>-0.000909</v>
       </c>

--- a/output/pdf_financials_xlsx/ODV.xlsx
+++ b/output/pdf_financials_xlsx/ODV.xlsx
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.047382</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.026468</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.015786</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -2088,15 +2088,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P26" s="3" t="n">
+        <v>93.825395</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>178.203975</v>
       </c>
     </row>
     <row r="27">
@@ -2106,13 +2102,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.768138</v>
+        <v>-0.81552</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.397989</v>
+        <v>-0.424457</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.652497</v>
+        <v>-1.668283</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2236,13 +2232,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.768138</v>
+        <v>-0.81552</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.397989</v>
+        <v>-0.424457</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.652497</v>
+        <v>-1.668283</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2539,22 +2535,22 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5945319999999999</v>
+        <v>1.528634</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.619329</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.166183</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005375</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000117</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.162715</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2562,7 +2558,7 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>33.407</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>105.944</v>
@@ -2653,22 +2649,22 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.880482</v>
+        <v>1.814584</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.048913</v>
+        <v>0.668242</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.005712</v>
+        <v>0.160471</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005375</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000117</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.162715</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2676,7 +2672,7 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>33.407</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>105.944</v>
@@ -3337,22 +3333,22 @@
         <v>0.629686</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.964382</v>
+        <v>0.03028</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.6421289999999999</v>
+        <v>0.0228</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.174388</v>
+        <v>0.008205</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.005375</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.000117</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.162715</v>
+        <v>0</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -13606,7 +13602,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -15892,7 +15888,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -16684,7 +16680,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -18146,7 +18142,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -23084,7 +23080,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -35346,7 +35342,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -37862,7 +37862,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -40968,7 +40972,11 @@
           <t>Change in reclamation deposit</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -58252,7 +58260,11 @@
           <t>Refundable reclamation deposit</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
@@ -60604,7 +60616,7 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -68162,7 +68174,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E628" s="5" t="n">

--- a/output/pdf_financials_xlsx/ODV.xlsx
+++ b/output/pdf_financials_xlsx/ODV.xlsx
@@ -930,16 +930,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>64.355</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>28.56</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="10">
@@ -995,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>64.355</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>28.56</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="11">
@@ -59120,7 +59120,11 @@
           <t>Other operating costs 23</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -59182,16 +59186,16 @@
         </is>
       </c>
       <c r="Q533" s="5" t="n">
-        <v>-64.355</v>
+        <v>64.355</v>
       </c>
       <c r="R533" s="5" t="n">
-        <v>-28.56</v>
+        <v>28.56</v>
       </c>
       <c r="S533" s="5" t="n">
-        <v>-29</v>
+        <v>29</v>
       </c>
       <c r="T533" s="5" t="n">
-        <v>-46.86</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="534">

--- a/output/pdf_financials_xlsx/ODV.xlsx
+++ b/output/pdf_financials_xlsx/ODV.xlsx
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.339435</v>
+        <v>0.371649</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.221727</v>
@@ -1394,7 +1394,7 @@
         <v>-85.69499999999999</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-328.552</v>
+        <v>-168.946</v>
       </c>
     </row>
     <row r="17">
@@ -1447,19 +1447,19 @@
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>12.971</v>
+        <v>-12.971</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-1.706</v>
+        <v>1.706</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-22.517</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>56.605</v>
+        <v>0.648</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>159.54</v>
+        <v>-0.066</v>
       </c>
     </row>
     <row r="18">
@@ -2157,7 +2157,7 @@
         <v>-85.69499999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-328.552</v>
+        <v>-168.946</v>
       </c>
     </row>
     <row r="28">
@@ -2287,7 +2287,7 @@
         <v>-77.88200000000001</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-322.272</v>
+        <v>-162.666</v>
       </c>
     </row>
     <row r="30">
@@ -2364,7 +2364,7 @@
         <v>-1707.938596491228</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-908.3713850837139</v>
+        <v>-458.4982242516489</v>
       </c>
     </row>
     <row r="31">
@@ -2426,10 +2426,10 @@
         <v>-11.01668379079211</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-66.05402882315188</v>
+        <v>-0.7561701382811132</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-48.55852346051767</v>
+        <v>-0.0390657369810472</v>
       </c>
     </row>
     <row r="32">
@@ -4330,27 +4330,25 @@
         <v>0</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.664</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>13.565</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>11.756</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>18.057</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>10.58</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>14.842</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="65">
@@ -4501,27 +4499,25 @@
         <v>0</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.109</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>4.996</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>7.961</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>7.328</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>9.568</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>7.747</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>22.948</v>
       </c>
     </row>
     <row r="68">
@@ -4680,16 +4676,16 @@
         </is>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>8.103999999999999</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>1.208</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>1.049</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="Q70" s="3" t="n">
         <v>0</v>
@@ -4737,16 +4733,16 @@
         </is>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.61</v>
+        <v>9.714</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.663</v>
+        <v>5.871</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>11.821</v>
+        <v>12.87</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>40.314</v>
+        <v>40.675</v>
       </c>
       <c r="Q71" s="3" t="n">
         <v>0</v>
@@ -4965,16 +4961,16 @@
         </is>
       </c>
       <c r="M75" s="3" t="n">
-        <v>15.127</v>
+        <v>7.023</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>15.273</v>
+        <v>14.065</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>20.133</v>
+        <v>19.084</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>77.893</v>
+        <v>77.532</v>
       </c>
       <c r="Q75" s="3" t="n">
         <v>242.811</v>
@@ -5282,16 +5278,16 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.009459056970020644</v>
+        <v>0.02333097113669587</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.02447996670472623</v>
+        <v>0.02613377800047643</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.02998523551405702</v>
+        <v>0.0317778218281988</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.08109997914581979</v>
+        <v>0.08173261436064413</v>
       </c>
       <c r="Q80" s="1" t="inlineStr">
         <is>
@@ -6980,10 +6976,10 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.749</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>5.761</v>
       </c>
       <c r="O110" s="3" t="n">
         <v>0</v>
@@ -7200,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-0.222</v>
       </c>
       <c r="N114" s="3" t="n">
         <v>0</v>
@@ -12366,7 +12362,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -14276,7 +14276,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -40120,7 +40124,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -43828,7 +43836,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -44110,7 +44122,11 @@
           <t>Net gain on acquisition of investments</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -45736,7 +45752,11 @@
           <t>Private placements 21</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -53268,7 +53288,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -53936,7 +53960,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -55856,7 +55884,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -56624,7 +56656,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -58360,7 +58396,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E525" s="5" t="n">
         <v>0.024625</v>
       </c>
@@ -59962,7 +60002,11 @@
           <t>Income tax recovery (expense) 22</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E542" t="inlineStr">
         <is>
           <t>-</t>
@@ -62030,7 +62074,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -62698,7 +62746,11 @@
           <t>Income tax recovery (expense) 23</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E571" t="inlineStr">
         <is>
           <t>-</t>
@@ -69236,7 +69288,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E639" s="5" t="n">
         <v>0.005</v>
       </c>
@@ -69332,7 +69388,11 @@
           <t>Rent and office expenses (Note 5)</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E640" s="5" t="n">
         <v>0.027214</v>
       </c>
